--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -37042,12 +37042,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -37072,22 +37072,22 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R221" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -37120,42 +37120,42 @@
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37187,12 +37187,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -37239,87 +37239,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="AA222" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ222" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr"/>
       <c r="AT222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -37346,7 +37327,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -37395,98 +37376,23 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
+      <c r="R223" t="n">
+        <v>0</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U223" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="W223" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X223" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD223" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE223" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF223" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG223" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH223" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI223" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ223" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK223" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
-        </is>
-      </c>
-      <c r="AM223" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN223" t="b">
-        <v>1</v>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
@@ -37585,123 +37491,362 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN224" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="AT224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA224" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
+      <c r="F225" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
+      <c r="G225" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>D052</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
         <is>
           <t>基孔肯雅热</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
+      <c r="K225" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
+      <c r="L225" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr">
+      <c r="M225" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N224" t="n">
-        <v>0</v>
-      </c>
-      <c r="O224" t="n">
-        <v>0</v>
-      </c>
-      <c r="R224" t="n">
-        <v>0</v>
-      </c>
-      <c r="S224" t="inlineStr">
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO224" t="inlineStr">
+      <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP224" t="inlineStr">
+      <c r="AP225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR224" t="inlineStr">
+      <c r="AR225" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS224" t="inlineStr"/>
-      <c r="AT224" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU224" t="inlineStr">
+      <c r="AS225" t="inlineStr"/>
+      <c r="AT225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU225" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV224" t="inlineStr">
+      <c r="AV225" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW224" t="inlineStr">
+      <c r="AW225" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX224" t="inlineStr">
+      <c r="AX225" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY224" t="inlineStr">
+      <c r="AY225" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ224" t="inlineStr">
+      <c r="AZ225" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA224" t="inlineStr">
+      <c r="BA225" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB224" t="inlineStr">
+      <c r="BB225" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC224" t="inlineStr">
+      <c r="BC225" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -37823,7 +37968,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -37833,7 +37978,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -37885,7 +38030,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>122742</v>
+        <v>122743</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -32942,13 +32942,13 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O196" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R196" t="n">
-        <v>0.01469124727807916</v>
+        <v>0.01101843545855937</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>122743</v>
+        <v>122742</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -28930,13 +28930,13 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>11345</v>
+        <v>11649</v>
       </c>
       <c r="O172" t="n">
-        <v>11345</v>
+        <v>11649</v>
       </c>
       <c r="R172" t="n">
-        <v>5.31225807671773</v>
+        <v>5.454605053828544</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -33797,13 +33797,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>6520</v>
+        <v>7678</v>
       </c>
       <c r="O202" t="n">
-        <v>6520</v>
+        <v>7678</v>
       </c>
       <c r="R202" t="n">
-        <v>3.052968061718784</v>
+        <v>3.595197665318531</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -33903,12 +33903,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -33942,100 +33942,84 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>1</v>
+        <v>529</v>
       </c>
       <c r="O203" t="n">
-        <v>1</v>
+        <v>529</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03744035142020597</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR203" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -34062,7 +34046,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -34111,98 +34095,23 @@
       <c r="O204" t="n">
         <v>1</v>
       </c>
+      <c r="R204" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U204" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN204" t="b">
-        <v>1</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
@@ -34301,17 +34210,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -34350,76 +34259,170 @@
       <c r="O205" t="n">
         <v>1</v>
       </c>
-      <c r="R205" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR205" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -34451,12 +34454,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -34496,7 +34499,7 @@
         <v>1</v>
       </c>
       <c r="R206" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -34529,42 +34532,42 @@
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -34596,12 +34599,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -34626,7 +34629,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -34635,13 +34638,13 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -34674,42 +34677,42 @@
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -34741,12 +34744,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -34785,9 +34788,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="P208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -34796,77 +34796,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA208" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34893,7 +34884,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -34945,98 +34936,18 @@
       <c r="P209" t="n">
         <v>0</v>
       </c>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD209" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE209" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG209" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN209" t="b">
-        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
@@ -35130,17 +35041,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -35165,7 +35076,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -35179,76 +35090,168 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="R210" t="n">
-        <v>0</v>
-      </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN210" t="b">
+        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35280,12 +35283,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -35324,9 +35327,6 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="P211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -35335,77 +35335,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA211" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ211" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr"/>
       <c r="AT211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35432,7 +35423,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -35484,98 +35475,18 @@
       <c r="P212" t="n">
         <v>0</v>
       </c>
-      <c r="U212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD212" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE212" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF212" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG212" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN212" t="b">
-        <v>1</v>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
@@ -35669,17 +35580,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -35704,7 +35615,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -35713,81 +35624,173 @@
         </is>
       </c>
       <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN213" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="AT213" t="n">
         <v>2</v>
       </c>
-      <c r="O213" t="n">
-        <v>2</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO213" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP213" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
-      <c r="AT213" t="n">
-        <v>0</v>
-      </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35819,12 +35822,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -35849,7 +35852,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -35858,13 +35861,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -35897,42 +35900,42 @@
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35964,12 +35967,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -36008,9 +36011,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="P215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -36019,77 +36019,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA215" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ215" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36116,7 +36107,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -36168,98 +36159,18 @@
       <c r="P216" t="n">
         <v>0</v>
       </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V216" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W216" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X216" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y216" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R216" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD216" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE216" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF216" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG216" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH216" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ216" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK216" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM216" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN216" t="b">
-        <v>1</v>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
@@ -36353,17 +36264,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -36388,7 +36299,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -36397,81 +36308,173 @@
         </is>
       </c>
       <c r="N217" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN217" t="b">
         <v>1</v>
       </c>
-      <c r="O217" t="n">
-        <v>1</v>
-      </c>
-      <c r="R217" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
       <c r="AT217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36503,12 +36506,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -36533,7 +36536,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -36542,13 +36545,13 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -36581,42 +36584,42 @@
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36648,12 +36651,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -36692,9 +36695,6 @@
       <c r="O219" t="n">
         <v>0</v>
       </c>
-      <c r="P219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0</v>
       </c>
@@ -36703,77 +36703,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA219" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ219" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr"/>
       <c r="AT219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36800,7 +36791,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -36852,98 +36843,18 @@
       <c r="P220" t="n">
         <v>0</v>
       </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W220" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X220" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y220" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R220" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD220" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE220" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF220" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG220" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH220" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI220" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ220" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM220" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN220" t="b">
-        <v>1</v>
       </c>
       <c r="AO220" t="inlineStr">
         <is>
@@ -37037,17 +36948,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -37072,7 +36983,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -37081,81 +36992,173 @@
         </is>
       </c>
       <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN221" t="b">
         <v>1</v>
       </c>
-      <c r="O221" t="n">
-        <v>1</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
       <c r="AT221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37187,12 +37190,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -37217,22 +37220,22 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R222" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -37265,42 +37268,42 @@
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37332,12 +37335,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -37362,12 +37365,12 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N223" t="n">
@@ -37376,6 +37379,9 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -37384,14 +37390,9 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
@@ -37401,22 +37402,17 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1185</t>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
         </is>
       </c>
       <c r="AT223" t="n">
@@ -37424,47 +37420,47 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37496,12 +37492,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -37526,12 +37522,12 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N224" t="n">
@@ -37540,19 +37536,22 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
+      <c r="P224" t="n">
+        <v>0</v>
+      </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1185</t>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
         </is>
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1185</t>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X224" t="inlineStr">
@@ -37567,12 +37566,12 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
@@ -37582,7 +37581,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr">
@@ -37617,12 +37616,12 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM224" t="inlineStr">
@@ -37640,22 +37639,17 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1185</t>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
         </is>
       </c>
       <c r="AT224" t="n">
@@ -37663,47 +37657,47 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37735,12 +37729,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -37813,40 +37807,733 @@
       </c>
       <c r="AV225" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA225" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB225" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC225" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>451</v>
+      </c>
+      <c r="O226" t="n">
+        <v>451</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0.211179232490057</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr"/>
+      <c r="AT226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU226" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV226" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA226" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB226" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC226" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="AT227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV227" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA227" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB227" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC227" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN228" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="AT228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV228" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA228" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB228" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC228" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>0</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="R229" t="n">
+        <v>0</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP229" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr"/>
+      <c r="AT229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU229" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV229" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW225" t="inlineStr">
+      <c r="AW229" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX225" t="inlineStr">
+      <c r="AX229" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY225" t="inlineStr">
+      <c r="AY229" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ225" t="inlineStr">
+      <c r="AZ229" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA225" t="inlineStr">
+      <c r="BA229" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB225" t="inlineStr">
+      <c r="BB229" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC225" t="inlineStr">
+      <c r="BC229" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -37968,7 +38655,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -37978,7 +38665,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -37998,7 +38685,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -38030,7 +38717,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>122742</v>
+        <v>125184</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -38539,6 +38539,151 @@
         </is>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N230" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO230" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP230" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr"/>
+      <c r="AT230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV230" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA230" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB230" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC230" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38572,7 +38717,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -38655,7 +38800,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -38665,7 +38810,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -28930,13 +28930,13 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>11649</v>
+        <v>11782</v>
       </c>
       <c r="O172" t="n">
-        <v>11649</v>
+        <v>11782</v>
       </c>
       <c r="R172" t="n">
-        <v>5.454605053828544</v>
+        <v>5.516881856314526</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -33797,13 +33797,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>7678</v>
+        <v>8213</v>
       </c>
       <c r="O202" t="n">
-        <v>7678</v>
+        <v>8213</v>
       </c>
       <c r="R202" t="n">
-        <v>3.595197665318531</v>
+        <v>3.845709615168155</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -37913,13 +37913,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>451</v>
+        <v>1384</v>
       </c>
       <c r="O226" t="n">
-        <v>451</v>
+        <v>1384</v>
       </c>
       <c r="R226" t="n">
-        <v>0.211179232490057</v>
+        <v>0.648053343162392</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>125184</v>
+        <v>126785</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -38684,6 +38684,400 @@
         </is>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>0</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" t="n">
+        <v>0</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="AT231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU231" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV231" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA231" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB231" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC231" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>0</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM232" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN232" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="AT232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV232" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA232" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB232" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC232" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38800,7 +39194,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -38810,7 +39204,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -38830,7 +39224,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -28930,13 +28930,13 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>11782</v>
+        <v>11872</v>
       </c>
       <c r="O172" t="n">
-        <v>11782</v>
+        <v>11872</v>
       </c>
       <c r="R172" t="n">
-        <v>5.516881856314526</v>
+        <v>5.559024053485491</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -33797,13 +33797,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>8213</v>
+        <v>8691</v>
       </c>
       <c r="O202" t="n">
-        <v>8213</v>
+        <v>8691</v>
       </c>
       <c r="R202" t="n">
-        <v>3.845709615168155</v>
+        <v>4.069531506809501</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -34454,12 +34454,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -34493,13 +34493,13 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -34532,42 +34532,42 @@
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -34599,12 +34599,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -34644,7 +34644,7 @@
         <v>1</v>
       </c>
       <c r="R207" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -34677,42 +34677,42 @@
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -34744,12 +34744,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -34774,7 +34774,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -34783,13 +34783,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -34822,42 +34822,42 @@
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -34889,12 +34889,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -34933,9 +34933,6 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="P209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
@@ -34944,77 +34941,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA209" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ209" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr"/>
       <c r="AT209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35041,7 +35029,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -35093,98 +35081,18 @@
       <c r="P210" t="n">
         <v>0</v>
       </c>
-      <c r="U210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD210" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE210" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF210" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG210" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM210" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN210" t="b">
-        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
@@ -35278,17 +35186,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -35313,7 +35221,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -35327,76 +35235,168 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="R211" t="n">
-        <v>0</v>
-      </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35428,12 +35428,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -35472,9 +35472,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="P212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -35483,77 +35480,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA212" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ212" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35580,7 +35568,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -35632,98 +35620,18 @@
       <c r="P213" t="n">
         <v>0</v>
       </c>
-      <c r="U213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W213" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD213" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE213" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF213" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG213" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ213" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK213" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM213" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN213" t="b">
-        <v>1</v>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
@@ -35817,17 +35725,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -35852,7 +35760,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -35861,81 +35769,173 @@
         </is>
       </c>
       <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN214" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO214" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP214" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="AT214" t="n">
         <v>2</v>
       </c>
-      <c r="O214" t="n">
-        <v>2</v>
-      </c>
-      <c r="R214" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO214" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP214" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr"/>
-      <c r="AT214" t="n">
-        <v>0</v>
-      </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35967,12 +35967,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -35997,7 +35997,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -36045,42 +36045,42 @@
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36112,12 +36112,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -36156,9 +36156,6 @@
       <c r="O216" t="n">
         <v>0</v>
       </c>
-      <c r="P216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0</v>
       </c>
@@ -36167,77 +36164,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA216" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ216" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36264,7 +36252,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -36316,98 +36304,18 @@
       <c r="P217" t="n">
         <v>0</v>
       </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y217" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R217" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD217" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE217" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF217" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG217" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN217" t="b">
-        <v>1</v>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
@@ -36501,17 +36409,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -36536,7 +36444,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -36545,81 +36453,173 @@
         </is>
       </c>
       <c r="N218" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN218" t="b">
         <v>1</v>
       </c>
-      <c r="O218" t="n">
-        <v>1</v>
-      </c>
-      <c r="R218" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
       <c r="AT218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36651,12 +36651,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -36681,7 +36681,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -36690,13 +36690,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R219" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -36729,42 +36729,42 @@
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36796,12 +36796,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -36840,9 +36840,6 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="P220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -36851,77 +36848,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA220" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ220" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36948,7 +36936,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -37000,98 +36988,18 @@
       <c r="P221" t="n">
         <v>0</v>
       </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD221" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE221" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF221" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG221" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH221" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI221" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ221" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK221" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM221" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN221" t="b">
-        <v>1</v>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
@@ -37185,17 +37093,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -37220,7 +37128,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -37229,81 +37137,173 @@
         </is>
       </c>
       <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN222" t="b">
         <v>1</v>
       </c>
-      <c r="O222" t="n">
-        <v>1</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
       <c r="AT222" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37335,12 +37335,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -37374,93 +37374,81 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O223" t="n">
-        <v>0</v>
-      </c>
-      <c r="P223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R223" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA223" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ223" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37487,7 +37475,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -37539,98 +37527,18 @@
       <c r="P224" t="n">
         <v>0</v>
       </c>
-      <c r="U224" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X224" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y224" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD224" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE224" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF224" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG224" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH224" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI224" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ224" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK224" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM224" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN224" t="b">
-        <v>1</v>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
@@ -37724,17 +37632,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -37759,12 +37667,12 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N225" t="n">
@@ -37773,76 +37681,168 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
-      <c r="R225" t="n">
-        <v>0</v>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM225" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN225" t="b">
+        <v>1</v>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37874,12 +37874,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -37913,13 +37913,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>1384</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
-        <v>1384</v>
+        <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>0.648053343162392</v>
+        <v>0</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -37952,42 +37952,42 @@
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38019,12 +38019,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -38058,100 +38058,81 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>2846</v>
       </c>
       <c r="O227" t="n">
-        <v>0</v>
+        <v>2846</v>
       </c>
       <c r="R227" t="n">
-        <v>0</v>
+        <v>1.332629923872954</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="AA227" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ227" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr"/>
       <c r="AT227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -38178,7 +38159,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -38222,103 +38203,28 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O228" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U228" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
-      <c r="V228" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="W228" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X228" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y228" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD228" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE228" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF228" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG228" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH228" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI228" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ228" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK228" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
-        </is>
-      </c>
-      <c r="AM228" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN228" t="b">
-        <v>1</v>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
@@ -38417,17 +38323,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -38461,81 +38367,175 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O229" t="n">
-        <v>0</v>
-      </c>
-      <c r="R229" t="n">
-        <v>0</v>
-      </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
+        </is>
+      </c>
+      <c r="AM229" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN229" t="b">
+        <v>1</v>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
       <c r="AT229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -38567,12 +38567,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -38597,7 +38597,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -38645,42 +38645,42 @@
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -38712,12 +38712,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -38756,9 +38756,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="P231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -38767,77 +38764,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA231" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ231" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
       <c r="AT231" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38864,7 +38852,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -38916,98 +38904,18 @@
       <c r="P232" t="n">
         <v>0</v>
       </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R232" t="n">
+        <v>0</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD232" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE232" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF232" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG232" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ232" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK232" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM232" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN232" t="b">
-        <v>1</v>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
@@ -39073,6 +38981,782 @@
         </is>
       </c>
       <c r="BC232" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N233" t="n">
+        <v>0</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM233" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN233" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO233" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP233" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="AT233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU233" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV233" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA233" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB233" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC233" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO234" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP234" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr"/>
+      <c r="AT234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU234" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV234" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA234" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB234" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC234" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N235" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO235" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP235" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="AT235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU235" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV235" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA235" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB235" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC235" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N236" t="n">
+        <v>0</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="n">
+        <v>0</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM236" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN236" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO236" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP236" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="AT236" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU236" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV236" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA236" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB236" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC236" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -39111,7 +39795,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -39194,7 +39878,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -39204,7 +39888,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -39224,7 +39908,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -39256,7 +39940,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>126785</v>
+        <v>128816</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -41207,13 +41207,13 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>8691</v>
+        <v>8912</v>
       </c>
       <c r="O240" t="n">
-        <v>8691</v>
+        <v>8912</v>
       </c>
       <c r="R240" t="n">
-        <v>4.069531506809501</v>
+        <v>4.173014013195981</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -48198,13 +48198,13 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>2846</v>
+        <v>4420</v>
       </c>
       <c r="O279" t="n">
-        <v>2846</v>
+        <v>4420</v>
       </c>
       <c r="R279" t="n">
-        <v>1.332629923872954</v>
+        <v>2.069650127729605</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
@@ -49899,6 +49899,1093 @@
       <c r="BC288" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>0</v>
+      </c>
+      <c r="O289" t="n">
+        <v>0</v>
+      </c>
+      <c r="R289" t="n">
+        <v>0</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO289" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP289" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR289" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS289" t="inlineStr"/>
+      <c r="AT289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV289" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA289" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB289" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC289" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>0</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0</v>
+      </c>
+      <c r="P290" t="n">
+        <v>0</v>
+      </c>
+      <c r="R290" t="n">
+        <v>0</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP290" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ290" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS290" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="AT290" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU290" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV290" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW290" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX290" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY290" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA290" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB290" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC290" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>0</v>
+      </c>
+      <c r="O291" t="n">
+        <v>0</v>
+      </c>
+      <c r="P291" t="n">
+        <v>0</v>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB291" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC291" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD291" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF291" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG291" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH291" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI291" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ291" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK291" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM291" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN291" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO291" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP291" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ291" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS291" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="AT291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU291" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV291" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW291" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX291" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY291" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA291" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB291" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC291" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N292" t="n">
+        <v>0</v>
+      </c>
+      <c r="O292" t="n">
+        <v>0</v>
+      </c>
+      <c r="R292" t="n">
+        <v>0</v>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO292" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP292" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ292" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR292" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS292" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="AT292" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU292" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV292" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW292" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX292" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY292" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA292" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB292" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC292" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N293" t="n">
+        <v>0</v>
+      </c>
+      <c r="O293" t="n">
+        <v>0</v>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB293" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC293" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD293" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE293" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF293" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG293" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH293" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI293" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ293" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK293" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
+        </is>
+      </c>
+      <c r="AM293" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN293" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO293" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP293" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ293" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR293" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS293" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="AT293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU293" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV293" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW293" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX293" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY293" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA293" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB293" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC293" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N294" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" t="n">
+        <v>0</v>
+      </c>
+      <c r="R294" t="n">
+        <v>0</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO294" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP294" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR294" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS294" t="inlineStr"/>
+      <c r="AT294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU294" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV294" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW294" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX294" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY294" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA294" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB294" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC294" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -49935,7 +51022,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -50018,7 +51105,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
@@ -50028,7 +51115,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11">
@@ -50048,7 +51135,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -50080,7 +51167,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>129531</v>
+        <v>131326</v>
       </c>
     </row>
     <row r="16">
